--- a/src/src/main/webapp/portal/zkb/engineer/APM_ZKB_Engineer_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/engineer/APM_ZKB_Engineer_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E8CA6C-8F1E-4C9B-AAE1-56CC1A0913FD}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618B6451-A825-4BD4-8374-5B508A1AA484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-16335" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="智康保工程师" sheetId="1" r:id="rId1"/>
@@ -35,12 +35,6 @@
     <t>邮箱</t>
   </si>
   <si>
-    <t>认证状态</t>
-  </si>
-  <si>
-    <t>年龄</t>
-  </si>
-  <si>
     <t>学历</t>
   </si>
   <si>
@@ -60,25 +54,25 @@
   </si>
   <si>
     <t>工作年限</t>
+  </si>
+  <si>
+    <t>身份证号</t>
+  </si>
+  <si>
+    <t>SSO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.3"/>
-      <color rgb="FF6A8759"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -103,12 +97,10 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -387,43 +379,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="7" width="30.44140625" customWidth="1"/>
+    <col min="8" max="8" width="28.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -435,17 +430,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0492F039-4FD5-4A0F-AC97-726D701B2292}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
@@ -455,16 +451,16 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
